--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32EBA32-ADA4-4B1A-B608-BE1C1742AD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD63DD7-41B7-41D6-8FDA-1853CA0BBAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>nama</t>
   </si>
   <si>
-    <t>tgl _lahir</t>
-  </si>
-  <si>
     <t>matematika</t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>2016-10-01</t>
+  </si>
+  <si>
+    <t>tgl_lahir</t>
   </si>
 </sst>
 </file>
@@ -653,33 +653,33 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>88</v>
@@ -699,13 +699,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>88</v>
@@ -725,13 +725,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>88</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5">
         <v>88</v>
@@ -777,13 +777,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>88</v>
@@ -803,13 +803,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>88</v>
@@ -829,13 +829,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>88</v>
@@ -855,13 +855,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>88</v>
@@ -881,13 +881,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>88</v>
@@ -907,13 +907,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>88</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12">
         <v>88</v>
@@ -959,13 +959,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <v>88</v>
@@ -985,13 +985,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14">
         <v>88</v>
@@ -1011,13 +1011,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15">
         <v>88</v>
@@ -1037,13 +1037,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16">
         <v>88</v>
@@ -1063,13 +1063,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17">
         <v>88</v>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18">
         <v>88</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19">
         <v>88</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20">
         <v>88</v>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21">
         <v>88</v>
@@ -1193,13 +1193,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22">
         <v>88</v>
@@ -1219,13 +1219,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>88</v>
@@ -1245,13 +1245,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24">
         <v>88</v>
@@ -1271,13 +1271,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25">
         <v>88</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26">
         <v>88</v>
@@ -1323,13 +1323,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27">
         <v>88</v>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD63DD7-41B7-41D6-8FDA-1853CA0BBAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFC0EA6-0E96-4B9F-B1FB-B30533AF510B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="14250" windowHeight="11250" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>nisn</t>
   </si>
@@ -51,12 +51,6 @@
     <t>ppkn</t>
   </si>
   <si>
-    <t>ipa</t>
-  </si>
-  <si>
-    <t>ips</t>
-  </si>
-  <si>
     <t>ABID AQILA PRANAJA</t>
   </si>
   <si>
@@ -286,6 +280,15 @@
   </si>
   <si>
     <t>tgl_lahir</t>
+  </si>
+  <si>
+    <t>ipas</t>
+  </si>
+  <si>
+    <t>pjok</t>
+  </si>
+  <si>
+    <t>seni_rupa</t>
   </si>
 </sst>
 </file>
@@ -638,14 +641,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C7160C-1724-4274-A0CF-AC33CF2F0F6D}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -665,385 +668,388 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>88</v>
+      </c>
+      <c r="E2">
+        <v>77</v>
+      </c>
+      <c r="F2">
+        <v>66</v>
+      </c>
+      <c r="G2">
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>88</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3">
+        <v>66</v>
+      </c>
+      <c r="G3">
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="D2">
-        <v>88</v>
-      </c>
-      <c r="E2">
-        <v>77</v>
-      </c>
-      <c r="F2">
-        <v>66</v>
-      </c>
-      <c r="G2">
-        <v>80</v>
-      </c>
-      <c r="H2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D4">
+        <v>88</v>
+      </c>
+      <c r="E4">
+        <v>77</v>
+      </c>
+      <c r="F4">
+        <v>66</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>60</v>
       </c>
-      <c r="D3">
-        <v>88</v>
-      </c>
-      <c r="E3">
-        <v>77</v>
-      </c>
-      <c r="F3">
-        <v>66</v>
-      </c>
-      <c r="G3">
-        <v>80</v>
-      </c>
-      <c r="H3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D5">
+        <v>88</v>
+      </c>
+      <c r="E5">
+        <v>77</v>
+      </c>
+      <c r="F5">
+        <v>66</v>
+      </c>
+      <c r="G5">
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>61</v>
       </c>
-      <c r="D4">
-        <v>88</v>
-      </c>
-      <c r="E4">
-        <v>77</v>
-      </c>
-      <c r="F4">
-        <v>66</v>
-      </c>
-      <c r="G4">
-        <v>80</v>
-      </c>
-      <c r="H4">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D6">
+        <v>88</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="F6">
+        <v>66</v>
+      </c>
+      <c r="G6">
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>62</v>
       </c>
-      <c r="D5">
-        <v>88</v>
-      </c>
-      <c r="E5">
-        <v>77</v>
-      </c>
-      <c r="F5">
-        <v>66</v>
-      </c>
-      <c r="G5">
-        <v>80</v>
-      </c>
-      <c r="H5">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D7">
+        <v>88</v>
+      </c>
+      <c r="E7">
+        <v>77</v>
+      </c>
+      <c r="F7">
+        <v>66</v>
+      </c>
+      <c r="G7">
+        <v>80</v>
+      </c>
+      <c r="H7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>63</v>
       </c>
-      <c r="D6">
-        <v>88</v>
-      </c>
-      <c r="E6">
-        <v>77</v>
-      </c>
-      <c r="F6">
-        <v>66</v>
-      </c>
-      <c r="G6">
-        <v>80</v>
-      </c>
-      <c r="H6">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D8">
+        <v>88</v>
+      </c>
+      <c r="E8">
+        <v>77</v>
+      </c>
+      <c r="F8">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>80</v>
+      </c>
+      <c r="H8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>64</v>
       </c>
-      <c r="D7">
-        <v>88</v>
-      </c>
-      <c r="E7">
-        <v>77</v>
-      </c>
-      <c r="F7">
-        <v>66</v>
-      </c>
-      <c r="G7">
-        <v>80</v>
-      </c>
-      <c r="H7">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D9">
+        <v>88</v>
+      </c>
+      <c r="E9">
+        <v>77</v>
+      </c>
+      <c r="F9">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="D8">
-        <v>88</v>
-      </c>
-      <c r="E8">
-        <v>77</v>
-      </c>
-      <c r="F8">
-        <v>66</v>
-      </c>
-      <c r="G8">
-        <v>80</v>
-      </c>
-      <c r="H8">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D10">
+        <v>88</v>
+      </c>
+      <c r="E10">
+        <v>77</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9">
-        <v>88</v>
-      </c>
-      <c r="E9">
-        <v>77</v>
-      </c>
-      <c r="F9">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>80</v>
-      </c>
-      <c r="H9">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11">
+        <v>88</v>
+      </c>
+      <c r="E11">
+        <v>77</v>
+      </c>
+      <c r="F11">
+        <v>66</v>
+      </c>
+      <c r="G11">
+        <v>80</v>
+      </c>
+      <c r="H11">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D10">
-        <v>88</v>
-      </c>
-      <c r="E10">
-        <v>77</v>
-      </c>
-      <c r="F10">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>80</v>
-      </c>
-      <c r="H10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D12">
+        <v>88</v>
+      </c>
+      <c r="E12">
+        <v>77</v>
+      </c>
+      <c r="F12">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+      <c r="H12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>68</v>
       </c>
-      <c r="D11">
-        <v>88</v>
-      </c>
-      <c r="E11">
-        <v>77</v>
-      </c>
-      <c r="F11">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>80</v>
-      </c>
-      <c r="H11">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D13">
+        <v>88</v>
+      </c>
+      <c r="E13">
+        <v>77</v>
+      </c>
+      <c r="F13">
+        <v>66</v>
+      </c>
+      <c r="G13">
+        <v>80</v>
+      </c>
+      <c r="H13">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>69</v>
       </c>
-      <c r="D12">
-        <v>88</v>
-      </c>
-      <c r="E12">
-        <v>77</v>
-      </c>
-      <c r="F12">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>80</v>
-      </c>
-      <c r="H12">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D14">
+        <v>88</v>
+      </c>
+      <c r="E14">
+        <v>77</v>
+      </c>
+      <c r="F14">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+      <c r="H14">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>70</v>
       </c>
-      <c r="D13">
-        <v>88</v>
-      </c>
-      <c r="E13">
-        <v>77</v>
-      </c>
-      <c r="F13">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>80</v>
-      </c>
-      <c r="H13">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D15">
+        <v>88</v>
+      </c>
+      <c r="E15">
+        <v>77</v>
+      </c>
+      <c r="F15">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>80</v>
+      </c>
+      <c r="H15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>71</v>
-      </c>
-      <c r="D14">
-        <v>88</v>
-      </c>
-      <c r="E14">
-        <v>77</v>
-      </c>
-      <c r="F14">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>80</v>
-      </c>
-      <c r="H14">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15">
-        <v>88</v>
-      </c>
-      <c r="E15">
-        <v>77</v>
-      </c>
-      <c r="F15">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>80</v>
-      </c>
-      <c r="H15">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
       </c>
       <c r="D16">
         <v>88</v>
@@ -1063,13 +1069,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17">
         <v>88</v>
@@ -1089,13 +1095,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D18">
         <v>88</v>
@@ -1115,13 +1121,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D19">
         <v>88</v>
@@ -1141,13 +1147,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D20">
         <v>88</v>
@@ -1167,13 +1173,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D21">
         <v>88</v>
@@ -1193,13 +1199,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22">
         <v>88</v>
@@ -1219,13 +1225,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23">
         <v>88</v>
@@ -1245,13 +1251,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D24">
         <v>88</v>
@@ -1271,13 +1277,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D25">
         <v>88</v>
@@ -1297,13 +1303,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D26">
         <v>88</v>
@@ -1323,13 +1329,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D27">
         <v>88</v>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFC0EA6-0E96-4B9F-B1FB-B30533AF510B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF25FA38-6A27-42BC-93DC-4E0182C24FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="14250" windowHeight="11250" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
   <si>
     <t>nisn</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>seni_rupa</t>
+  </si>
+  <si>
+    <t>kelas</t>
+  </si>
+  <si>
+    <t>2b</t>
   </si>
 </sst>
 </file>
@@ -641,715 +647,797 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C7160C-1724-4274-A0CF-AC33CF2F0F6D}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>82</v>
-      </c>
       <c r="H1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>57</v>
       </c>
-      <c r="D2">
-        <v>88</v>
-      </c>
       <c r="E2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>58</v>
       </c>
-      <c r="D3">
-        <v>88</v>
-      </c>
       <c r="E3">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F3">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>59</v>
       </c>
-      <c r="D4">
-        <v>88</v>
-      </c>
       <c r="E4">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H4">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>60</v>
       </c>
-      <c r="D5">
-        <v>88</v>
-      </c>
       <c r="E5">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F5">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H5">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>61</v>
       </c>
-      <c r="D6">
-        <v>88</v>
-      </c>
       <c r="E6">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F6">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H6">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>62</v>
       </c>
-      <c r="D7">
-        <v>88</v>
-      </c>
       <c r="E7">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F7">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H7">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>63</v>
       </c>
-      <c r="D8">
-        <v>88</v>
-      </c>
       <c r="E8">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G8">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H8">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="D9">
-        <v>88</v>
-      </c>
       <c r="E9">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F9">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G9">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H9">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I9">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>65</v>
       </c>
-      <c r="D10">
-        <v>88</v>
-      </c>
       <c r="E10">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G10">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11">
-        <v>88</v>
+      <c r="D11" t="s">
+        <v>66</v>
       </c>
       <c r="E11">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F11">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H11">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I11">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>67</v>
       </c>
-      <c r="D12">
-        <v>88</v>
-      </c>
       <c r="E12">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G12">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H12">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="D13">
-        <v>88</v>
-      </c>
       <c r="E13">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H13">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I13">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>69</v>
       </c>
-      <c r="D14">
-        <v>88</v>
-      </c>
       <c r="E14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F14">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G14">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H14">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>70</v>
       </c>
-      <c r="D15">
-        <v>88</v>
-      </c>
       <c r="E15">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G15">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H15">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>71</v>
       </c>
-      <c r="D16">
-        <v>88</v>
-      </c>
       <c r="E16">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F16">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G16">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H16">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>72</v>
       </c>
-      <c r="D17">
-        <v>88</v>
-      </c>
       <c r="E17">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F17">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H17">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I17">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
         <v>47</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>70</v>
       </c>
-      <c r="D18">
-        <v>88</v>
-      </c>
       <c r="E18">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F18">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G18">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H18">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I18">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>73</v>
       </c>
-      <c r="D19">
-        <v>88</v>
-      </c>
       <c r="E19">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F19">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H19">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>72</v>
       </c>
-      <c r="D20">
-        <v>88</v>
-      </c>
       <c r="E20">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G20">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H20">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I20">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
         <v>50</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>74</v>
       </c>
-      <c r="D21">
-        <v>88</v>
-      </c>
       <c r="E21">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F21">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G21">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H21">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I21">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>75</v>
       </c>
-      <c r="D22">
-        <v>88</v>
-      </c>
       <c r="E22">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F22">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G22">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H22">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>76</v>
       </c>
-      <c r="D23">
-        <v>88</v>
-      </c>
       <c r="E23">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F23">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G23">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H23">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I23">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
         <v>53</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24">
-        <v>88</v>
+      <c r="D24" t="s">
+        <v>77</v>
       </c>
       <c r="E24">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G24">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I24">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>78</v>
       </c>
-      <c r="D25">
-        <v>88</v>
-      </c>
       <c r="E25">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F25">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G25">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H25">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>79</v>
       </c>
-      <c r="D26">
-        <v>88</v>
-      </c>
       <c r="E26">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F26">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G26">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H26">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="I26">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
         <v>56</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27">
-        <v>88</v>
+      <c r="D27" t="s">
+        <v>80</v>
       </c>
       <c r="E27">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F27">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G27">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H27">
+        <v>80</v>
+      </c>
+      <c r="I27">
         <v>82</v>
       </c>
     </row>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF25FA38-6A27-42BC-93DC-4E0182C24FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245C6743-40C0-41DD-8C94-5D4C56FD2A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
+    <workbookView xWindow="14610" yWindow="555" windowWidth="14250" windowHeight="11250" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
   <si>
     <t>nisn</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>2b</t>
+  </si>
+  <si>
+    <t>pin</t>
   </si>
 </sst>
 </file>
@@ -647,15 +650,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C7160C-1724-4274-A0CF-AC33CF2F0F6D}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -666,28 +670,31 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
         <v>81</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>82</v>
-      </c>
       <c r="I1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" t="s">
         <v>83</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -697,26 +704,30 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="str">
+        <f>RIGHT(B2,4)</f>
+        <v>2347</v>
+      </c>
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="E2">
-        <v>88</v>
-      </c>
       <c r="F2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -726,26 +737,30 @@
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D27" si="0">RIGHT(B3,4)</f>
+        <v>9362</v>
+      </c>
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="E3">
-        <v>88</v>
-      </c>
       <c r="F3">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H3">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -755,26 +770,30 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>1612</v>
+      </c>
+      <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="E4">
-        <v>88</v>
-      </c>
       <c r="F4">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H4">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -784,26 +803,30 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>8262</v>
+      </c>
+      <c r="E5" t="s">
         <v>60</v>
       </c>
-      <c r="E5">
-        <v>88</v>
-      </c>
       <c r="F5">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H5">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I5">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -813,26 +836,30 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>4061</v>
+      </c>
+      <c r="E6" t="s">
         <v>61</v>
       </c>
-      <c r="E6">
-        <v>88</v>
-      </c>
       <c r="F6">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G6">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I6">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -842,26 +869,30 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>6322</v>
+      </c>
+      <c r="E7" t="s">
         <v>62</v>
       </c>
-      <c r="E7">
-        <v>88</v>
-      </c>
       <c r="F7">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I7">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -871,26 +902,30 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>4439</v>
+      </c>
+      <c r="E8" t="s">
         <v>63</v>
       </c>
-      <c r="E8">
-        <v>88</v>
-      </c>
       <c r="F8">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G8">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I8">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -900,26 +935,30 @@
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>6537</v>
+      </c>
+      <c r="E9" t="s">
         <v>64</v>
       </c>
-      <c r="E9">
-        <v>88</v>
-      </c>
       <c r="F9">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G9">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I9">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J9">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -929,26 +968,30 @@
       <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>9239</v>
+      </c>
+      <c r="E10" t="s">
         <v>65</v>
       </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
       <c r="F10">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H10">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -958,26 +1001,30 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11">
-        <v>88</v>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>9500</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G11">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H11">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I11">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -987,26 +1034,30 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>4569</v>
+      </c>
+      <c r="E12" t="s">
         <v>67</v>
       </c>
-      <c r="E12">
-        <v>88</v>
-      </c>
       <c r="F12">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G12">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H12">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I12">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -1016,26 +1067,30 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>7955</v>
+      </c>
+      <c r="E13" t="s">
         <v>68</v>
       </c>
-      <c r="E13">
-        <v>88</v>
-      </c>
       <c r="F13">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G13">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I13">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J13">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -1045,26 +1100,30 @@
       <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>3253</v>
+      </c>
+      <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="E14">
-        <v>88</v>
-      </c>
       <c r="F14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G14">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I14">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J14">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -1074,26 +1133,30 @@
       <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>0606</v>
+      </c>
+      <c r="E15" t="s">
         <v>70</v>
       </c>
-      <c r="E15">
-        <v>88</v>
-      </c>
       <c r="F15">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G15">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H15">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I15">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1103,26 +1166,30 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>3334</v>
+      </c>
+      <c r="E16" t="s">
         <v>71</v>
       </c>
-      <c r="E16">
-        <v>88</v>
-      </c>
       <c r="F16">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G16">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H16">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I16">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J16">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -1132,26 +1199,30 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>0746</v>
+      </c>
+      <c r="E17" t="s">
         <v>72</v>
       </c>
-      <c r="E17">
-        <v>88</v>
-      </c>
       <c r="F17">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G17">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H17">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I17">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J17">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -1161,26 +1232,30 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>1962</v>
+      </c>
+      <c r="E18" t="s">
         <v>70</v>
       </c>
-      <c r="E18">
-        <v>88</v>
-      </c>
       <c r="F18">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G18">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H18">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I18">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J18">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1190,26 +1265,30 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>4992</v>
+      </c>
+      <c r="E19" t="s">
         <v>73</v>
       </c>
-      <c r="E19">
-        <v>88</v>
-      </c>
       <c r="F19">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H19">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I19">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -1219,26 +1298,30 @@
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>9493</v>
+      </c>
+      <c r="E20" t="s">
         <v>72</v>
       </c>
-      <c r="E20">
-        <v>88</v>
-      </c>
       <c r="F20">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G20">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H20">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I20">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J20">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -1248,26 +1331,30 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>6980</v>
+      </c>
+      <c r="E21" t="s">
         <v>74</v>
       </c>
-      <c r="E21">
-        <v>88</v>
-      </c>
       <c r="F21">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G21">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H21">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I21">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J21">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1277,26 +1364,30 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>7896</v>
+      </c>
+      <c r="E22" t="s">
         <v>75</v>
       </c>
-      <c r="E22">
-        <v>88</v>
-      </c>
       <c r="F22">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G22">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H22">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I22">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -1306,26 +1397,30 @@
       <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>5908</v>
+      </c>
+      <c r="E23" t="s">
         <v>76</v>
       </c>
-      <c r="E23">
-        <v>88</v>
-      </c>
       <c r="F23">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G23">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H23">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I23">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J23">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -1335,26 +1430,30 @@
       <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24">
-        <v>88</v>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>3584</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
       </c>
       <c r="F24">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G24">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J24">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -1364,26 +1463,30 @@
       <c r="C25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>5018</v>
+      </c>
+      <c r="E25" t="s">
         <v>78</v>
       </c>
-      <c r="E25">
-        <v>88</v>
-      </c>
       <c r="F25">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H25">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I25">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -1393,26 +1496,30 @@
       <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>4346</v>
+      </c>
+      <c r="E26" t="s">
         <v>79</v>
       </c>
-      <c r="E26">
-        <v>88</v>
-      </c>
       <c r="F26">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H26">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I26">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J26">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -1422,22 +1529,26 @@
       <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="D27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27">
-        <v>88</v>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>5001</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
       </c>
       <c r="F27">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I27">
+        <v>80</v>
+      </c>
+      <c r="J27">
         <v>82</v>
       </c>
     </row>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245C6743-40C0-41DD-8C94-5D4C56FD2A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C0453C-B27A-4950-B3B4-DB9C168E0F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14610" yWindow="555" windowWidth="14250" windowHeight="11250" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
@@ -334,8 +334,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,6 +654,7 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.140625" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -663,7 +665,7 @@
       <c r="A1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
@@ -698,14 +700,14 @@
       <c r="A2" t="s">
         <v>86</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="str">
-        <f>RIGHT(B2,4)</f>
+        <f>TEXT(RIGHT(B2,4),"0000")</f>
         <v>2347</v>
       </c>
       <c r="E2" t="s">
@@ -731,14 +733,14 @@
       <c r="A3" t="s">
         <v>86</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D27" si="0">RIGHT(B3,4)</f>
+        <f t="shared" ref="D3:D27" si="0">TEXT(RIGHT(B3,4),"0000")</f>
         <v>9362</v>
       </c>
       <c r="E3" t="s">
@@ -764,7 +766,7 @@
       <c r="A4" t="s">
         <v>86</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" t="s">
@@ -797,7 +799,7 @@
       <c r="A5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C5" t="s">
@@ -830,7 +832,7 @@
       <c r="A6" t="s">
         <v>86</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C6" t="s">
@@ -863,7 +865,7 @@
       <c r="A7" t="s">
         <v>86</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C7" t="s">
@@ -896,7 +898,7 @@
       <c r="A8" t="s">
         <v>86</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C8" t="s">
@@ -929,7 +931,7 @@
       <c r="A9" t="s">
         <v>86</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C9" t="s">
@@ -962,7 +964,7 @@
       <c r="A10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
@@ -995,7 +997,7 @@
       <c r="A11" t="s">
         <v>86</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C11" t="s">
@@ -1028,7 +1030,7 @@
       <c r="A12" t="s">
         <v>86</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C12" t="s">
@@ -1061,7 +1063,7 @@
       <c r="A13" t="s">
         <v>86</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C13" t="s">
@@ -1094,7 +1096,7 @@
       <c r="A14" t="s">
         <v>86</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C14" t="s">
@@ -1127,7 +1129,7 @@
       <c r="A15" t="s">
         <v>86</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C15" t="s">
@@ -1160,7 +1162,7 @@
       <c r="A16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C16" t="s">
@@ -1193,7 +1195,7 @@
       <c r="A17" t="s">
         <v>86</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C17" t="s">
@@ -1226,7 +1228,7 @@
       <c r="A18" t="s">
         <v>86</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C18" t="s">
@@ -1259,7 +1261,7 @@
       <c r="A19" t="s">
         <v>86</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C19" t="s">
@@ -1292,7 +1294,7 @@
       <c r="A20" t="s">
         <v>86</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C20" t="s">
@@ -1325,7 +1327,7 @@
       <c r="A21" t="s">
         <v>86</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
@@ -1358,7 +1360,7 @@
       <c r="A22" t="s">
         <v>86</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C22" t="s">
@@ -1391,7 +1393,7 @@
       <c r="A23" t="s">
         <v>86</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C23" t="s">
@@ -1424,7 +1426,7 @@
       <c r="A24" t="s">
         <v>86</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C24" t="s">
@@ -1457,7 +1459,7 @@
       <c r="A25" t="s">
         <v>86</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C25" t="s">
@@ -1490,7 +1492,7 @@
       <c r="A26" t="s">
         <v>86</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C26" t="s">
@@ -1523,7 +1525,7 @@
       <c r="A27" t="s">
         <v>86</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C27" t="s">

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C0453C-B27A-4950-B3B4-DB9C168E0F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C6B505-8A91-4EA2-A363-CE3BF545522E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14610" yWindow="555" windowWidth="14250" windowHeight="11250" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -656,7 +656,7 @@
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
   </cols>
@@ -671,7 +671,7 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E1" t="s">
@@ -706,7 +706,7 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" s="1" t="str">
         <f>TEXT(RIGHT(B2,4),"0000")</f>
         <v>2347</v>
       </c>
@@ -739,7 +739,7 @@
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="1" t="str">
         <f t="shared" ref="D3:D27" si="0">TEXT(RIGHT(B3,4),"0000")</f>
         <v>9362</v>
       </c>
@@ -772,7 +772,7 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1612</v>
       </c>
@@ -805,7 +805,7 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>8262</v>
       </c>
@@ -838,7 +838,7 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4061</v>
       </c>
@@ -871,7 +871,7 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>6322</v>
       </c>
@@ -904,7 +904,7 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4439</v>
       </c>
@@ -937,7 +937,7 @@
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>6537</v>
       </c>
@@ -970,7 +970,7 @@
       <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>9239</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>9500</v>
       </c>
@@ -1036,7 +1036,7 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4569</v>
       </c>
@@ -1069,7 +1069,7 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>7955</v>
       </c>
@@ -1102,7 +1102,7 @@
       <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3253</v>
       </c>
@@ -1135,7 +1135,7 @@
       <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0606</v>
       </c>
@@ -1168,7 +1168,7 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3334</v>
       </c>
@@ -1201,7 +1201,7 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0746</v>
       </c>
@@ -1234,7 +1234,7 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1962</v>
       </c>
@@ -1267,7 +1267,7 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4992</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>9493</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>6980</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>7896</v>
       </c>
@@ -1399,7 +1399,7 @@
       <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>5908</v>
       </c>
@@ -1432,7 +1432,7 @@
       <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3584</v>
       </c>
@@ -1465,7 +1465,7 @@
       <c r="C25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>5018</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4346</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>5001</v>
       </c>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C6B505-8A91-4EA2-A363-CE3BF545522E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32A4240-1FE6-4C06-94AC-01458239CD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="89">
   <si>
     <t>nisn</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>pin</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -334,9 +337,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -716,17 +720,20 @@
       <c r="F2">
         <v>88</v>
       </c>
-      <c r="G2">
-        <v>77</v>
-      </c>
-      <c r="H2">
-        <v>66</v>
-      </c>
-      <c r="I2">
-        <v>80</v>
-      </c>
-      <c r="J2">
-        <v>82</v>
+      <c r="G2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -749,17 +756,20 @@
       <c r="F3">
         <v>88</v>
       </c>
-      <c r="G3">
-        <v>77</v>
-      </c>
-      <c r="H3">
-        <v>66</v>
-      </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
-      <c r="J3">
-        <v>82</v>
+      <c r="G3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -782,17 +792,20 @@
       <c r="F4">
         <v>88</v>
       </c>
-      <c r="G4">
-        <v>77</v>
-      </c>
-      <c r="H4">
-        <v>66</v>
-      </c>
-      <c r="I4">
-        <v>80</v>
-      </c>
-      <c r="J4">
-        <v>82</v>
+      <c r="G4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -815,17 +828,20 @@
       <c r="F5">
         <v>88</v>
       </c>
-      <c r="G5">
-        <v>77</v>
-      </c>
-      <c r="H5">
-        <v>66</v>
-      </c>
-      <c r="I5">
-        <v>80</v>
-      </c>
-      <c r="J5">
-        <v>82</v>
+      <c r="G5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -848,17 +864,20 @@
       <c r="F6">
         <v>88</v>
       </c>
-      <c r="G6">
-        <v>77</v>
-      </c>
-      <c r="H6">
-        <v>66</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>82</v>
+      <c r="G6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -881,17 +900,20 @@
       <c r="F7">
         <v>88</v>
       </c>
-      <c r="G7">
-        <v>77</v>
-      </c>
-      <c r="H7">
-        <v>66</v>
-      </c>
-      <c r="I7">
-        <v>80</v>
-      </c>
-      <c r="J7">
-        <v>82</v>
+      <c r="G7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -914,17 +936,20 @@
       <c r="F8">
         <v>88</v>
       </c>
-      <c r="G8">
-        <v>77</v>
-      </c>
-      <c r="H8">
-        <v>66</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>82</v>
+      <c r="G8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -947,17 +972,20 @@
       <c r="F9">
         <v>88</v>
       </c>
-      <c r="G9">
-        <v>77</v>
-      </c>
-      <c r="H9">
-        <v>66</v>
-      </c>
-      <c r="I9">
-        <v>80</v>
-      </c>
-      <c r="J9">
-        <v>82</v>
+      <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -980,17 +1008,20 @@
       <c r="F10">
         <v>88</v>
       </c>
-      <c r="G10">
-        <v>77</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>80</v>
-      </c>
-      <c r="J10">
-        <v>82</v>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1013,17 +1044,20 @@
       <c r="F11">
         <v>88</v>
       </c>
-      <c r="G11">
-        <v>77</v>
-      </c>
-      <c r="H11">
-        <v>66</v>
-      </c>
-      <c r="I11">
-        <v>80</v>
-      </c>
-      <c r="J11">
-        <v>82</v>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1046,17 +1080,20 @@
       <c r="F12">
         <v>88</v>
       </c>
-      <c r="G12">
-        <v>77</v>
-      </c>
-      <c r="H12">
-        <v>66</v>
-      </c>
-      <c r="I12">
-        <v>80</v>
-      </c>
-      <c r="J12">
-        <v>82</v>
+      <c r="G12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1079,17 +1116,20 @@
       <c r="F13">
         <v>88</v>
       </c>
-      <c r="G13">
-        <v>77</v>
-      </c>
-      <c r="H13">
-        <v>66</v>
-      </c>
-      <c r="I13">
-        <v>80</v>
-      </c>
-      <c r="J13">
-        <v>82</v>
+      <c r="G13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1112,17 +1152,20 @@
       <c r="F14">
         <v>88</v>
       </c>
-      <c r="G14">
-        <v>77</v>
-      </c>
-      <c r="H14">
-        <v>66</v>
-      </c>
-      <c r="I14">
-        <v>80</v>
-      </c>
-      <c r="J14">
-        <v>82</v>
+      <c r="G14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1145,17 +1188,20 @@
       <c r="F15">
         <v>88</v>
       </c>
-      <c r="G15">
-        <v>77</v>
-      </c>
-      <c r="H15">
-        <v>66</v>
-      </c>
-      <c r="I15">
-        <v>80</v>
-      </c>
-      <c r="J15">
-        <v>82</v>
+      <c r="G15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1178,20 +1224,23 @@
       <c r="F16">
         <v>88</v>
       </c>
-      <c r="G16">
-        <v>77</v>
-      </c>
-      <c r="H16">
-        <v>66</v>
-      </c>
-      <c r="I16">
-        <v>80</v>
-      </c>
-      <c r="J16">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -1211,20 +1260,23 @@
       <c r="F17">
         <v>88</v>
       </c>
-      <c r="G17">
-        <v>77</v>
-      </c>
-      <c r="H17">
-        <v>66</v>
-      </c>
-      <c r="I17">
-        <v>80</v>
-      </c>
-      <c r="J17">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -1244,20 +1296,23 @@
       <c r="F18">
         <v>88</v>
       </c>
-      <c r="G18">
-        <v>77</v>
-      </c>
-      <c r="H18">
-        <v>66</v>
-      </c>
-      <c r="I18">
-        <v>80</v>
-      </c>
-      <c r="J18">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -1277,20 +1332,23 @@
       <c r="F19">
         <v>88</v>
       </c>
-      <c r="G19">
-        <v>77</v>
-      </c>
-      <c r="H19">
-        <v>66</v>
-      </c>
-      <c r="I19">
-        <v>80</v>
-      </c>
-      <c r="J19">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -1310,20 +1368,23 @@
       <c r="F20">
         <v>88</v>
       </c>
-      <c r="G20">
-        <v>77</v>
-      </c>
-      <c r="H20">
-        <v>66</v>
-      </c>
-      <c r="I20">
-        <v>80</v>
-      </c>
-      <c r="J20">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -1343,20 +1404,23 @@
       <c r="F21">
         <v>88</v>
       </c>
-      <c r="G21">
-        <v>77</v>
-      </c>
-      <c r="H21">
-        <v>66</v>
-      </c>
-      <c r="I21">
-        <v>80</v>
-      </c>
-      <c r="J21">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1376,20 +1440,23 @@
       <c r="F22">
         <v>88</v>
       </c>
-      <c r="G22">
-        <v>77</v>
-      </c>
-      <c r="H22">
-        <v>66</v>
-      </c>
-      <c r="I22">
-        <v>80</v>
-      </c>
-      <c r="J22">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -1409,20 +1476,23 @@
       <c r="F23">
         <v>88</v>
       </c>
-      <c r="G23">
-        <v>77</v>
-      </c>
-      <c r="H23">
-        <v>66</v>
-      </c>
-      <c r="I23">
-        <v>80</v>
-      </c>
-      <c r="J23">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -1442,20 +1512,23 @@
       <c r="F24">
         <v>88</v>
       </c>
-      <c r="G24">
-        <v>77</v>
-      </c>
-      <c r="H24">
-        <v>66</v>
-      </c>
-      <c r="I24">
-        <v>80</v>
-      </c>
-      <c r="J24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -1475,20 +1548,23 @@
       <c r="F25">
         <v>88</v>
       </c>
-      <c r="G25">
-        <v>77</v>
-      </c>
-      <c r="H25">
-        <v>66</v>
-      </c>
-      <c r="I25">
-        <v>80</v>
-      </c>
-      <c r="J25">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -1508,20 +1584,23 @@
       <c r="F26">
         <v>88</v>
       </c>
-      <c r="G26">
-        <v>77</v>
-      </c>
-      <c r="H26">
-        <v>66</v>
-      </c>
-      <c r="I26">
-        <v>80</v>
-      </c>
-      <c r="J26">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -1541,17 +1620,20 @@
       <c r="F27">
         <v>88</v>
       </c>
-      <c r="G27">
-        <v>77</v>
-      </c>
-      <c r="H27">
-        <v>66</v>
-      </c>
-      <c r="I27">
-        <v>80</v>
-      </c>
-      <c r="J27">
-        <v>82</v>
+      <c r="G27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143E54E-B885-41E4-8D0B-F7DB0C8110D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E62C870-CE19-4758-8D66-9CDA1DD5AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6001" uniqueCount="1466">
   <si>
     <t>nisn</t>
   </si>
@@ -4426,6 +4426,12 @@
   </si>
   <si>
     <t>0000000000</t>
+  </si>
+  <si>
+    <t>seni_musik</t>
+  </si>
+  <si>
+    <t>bahasa_inggris</t>
   </si>
 </sst>
 </file>
@@ -4780,7 +4786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C7160C-1724-4274-A0CF-AC33CF2F0F6D}">
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:M500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -4788,9 +4794,11 @@
     <col min="4" max="4" width="35.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -4824,8 +4832,14 @@
       <c r="K1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1447</v>
       </c>
@@ -4860,8 +4874,14 @@
       <c r="K2" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1447</v>
       </c>
@@ -4896,8 +4916,14 @@
       <c r="K3" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1447</v>
       </c>
@@ -4932,8 +4958,14 @@
       <c r="K4" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1447</v>
       </c>
@@ -4968,8 +5000,14 @@
       <c r="K5" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1447</v>
       </c>
@@ -5004,8 +5042,14 @@
       <c r="K6" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1447</v>
       </c>
@@ -5040,8 +5084,14 @@
       <c r="K7" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1447</v>
       </c>
@@ -5076,8 +5126,14 @@
       <c r="K8" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1447</v>
       </c>
@@ -5112,8 +5168,14 @@
       <c r="K9" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1447</v>
       </c>
@@ -5148,8 +5210,14 @@
       <c r="K10" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1447</v>
       </c>
@@ -5184,8 +5252,14 @@
       <c r="K11" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1447</v>
       </c>
@@ -5220,8 +5294,14 @@
       <c r="K12" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1447</v>
       </c>
@@ -5256,8 +5336,14 @@
       <c r="K13" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1447</v>
       </c>
@@ -5292,8 +5378,14 @@
       <c r="K14" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1447</v>
       </c>
@@ -5328,8 +5420,14 @@
       <c r="K15" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1447</v>
       </c>
@@ -5364,8 +5462,14 @@
       <c r="K16" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1447</v>
       </c>
@@ -5400,8 +5504,14 @@
       <c r="K17" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1447</v>
       </c>
@@ -5436,8 +5546,14 @@
       <c r="K18" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1447</v>
       </c>
@@ -5472,8 +5588,14 @@
       <c r="K19" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1447</v>
       </c>
@@ -5508,8 +5630,14 @@
       <c r="K20" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1447</v>
       </c>
@@ -5544,8 +5672,14 @@
       <c r="K21" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1447</v>
       </c>
@@ -5580,8 +5714,14 @@
       <c r="K22" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1447</v>
       </c>
@@ -5616,8 +5756,14 @@
       <c r="K23" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1447</v>
       </c>
@@ -5652,8 +5798,14 @@
       <c r="K24" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1447</v>
       </c>
@@ -5688,8 +5840,14 @@
       <c r="K25" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1447</v>
       </c>
@@ -5724,8 +5882,14 @@
       <c r="K26" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1447</v>
       </c>
@@ -5760,8 +5924,14 @@
       <c r="K27" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1447</v>
       </c>
@@ -5796,8 +5966,14 @@
       <c r="K28" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1447</v>
       </c>
@@ -5832,8 +6008,14 @@
       <c r="K29" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1448</v>
       </c>
@@ -5868,8 +6050,14 @@
       <c r="K30" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1448</v>
       </c>
@@ -5904,8 +6092,14 @@
       <c r="K31" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1448</v>
       </c>
@@ -5940,8 +6134,14 @@
       <c r="K32" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1448</v>
       </c>
@@ -5976,8 +6176,14 @@
       <c r="K33" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1448</v>
       </c>
@@ -6012,8 +6218,14 @@
       <c r="K34" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1448</v>
       </c>
@@ -6048,8 +6260,14 @@
       <c r="K35" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1448</v>
       </c>
@@ -6084,8 +6302,14 @@
       <c r="K36" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1448</v>
       </c>
@@ -6120,8 +6344,14 @@
       <c r="K37" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1448</v>
       </c>
@@ -6156,8 +6386,14 @@
       <c r="K38" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1448</v>
       </c>
@@ -6192,8 +6428,14 @@
       <c r="K39" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1448</v>
       </c>
@@ -6228,8 +6470,14 @@
       <c r="K40" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1448</v>
       </c>
@@ -6264,8 +6512,14 @@
       <c r="K41" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1448</v>
       </c>
@@ -6300,8 +6554,14 @@
       <c r="K42" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1448</v>
       </c>
@@ -6336,8 +6596,14 @@
       <c r="K43" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1448</v>
       </c>
@@ -6372,8 +6638,14 @@
       <c r="K44" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1448</v>
       </c>
@@ -6408,8 +6680,14 @@
       <c r="K45" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1448</v>
       </c>
@@ -6444,8 +6722,14 @@
       <c r="K46" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1448</v>
       </c>
@@ -6480,8 +6764,14 @@
       <c r="K47" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1448</v>
       </c>
@@ -6516,8 +6806,14 @@
       <c r="K48" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1448</v>
       </c>
@@ -6552,8 +6848,14 @@
       <c r="K49" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1448</v>
       </c>
@@ -6588,8 +6890,14 @@
       <c r="K50" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1448</v>
       </c>
@@ -6624,8 +6932,14 @@
       <c r="K51" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1448</v>
       </c>
@@ -6660,8 +6974,14 @@
       <c r="K52" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1448</v>
       </c>
@@ -6696,8 +7016,14 @@
       <c r="K53" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1448</v>
       </c>
@@ -6732,8 +7058,14 @@
       <c r="K54" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1448</v>
       </c>
@@ -6768,8 +7100,14 @@
       <c r="K55" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1448</v>
       </c>
@@ -6804,8 +7142,14 @@
       <c r="K56" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1449</v>
       </c>
@@ -6840,8 +7184,14 @@
       <c r="K57" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1449</v>
       </c>
@@ -6876,8 +7226,14 @@
       <c r="K58" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1449</v>
       </c>
@@ -6912,8 +7268,14 @@
       <c r="K59" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1449</v>
       </c>
@@ -6948,8 +7310,14 @@
       <c r="K60" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1449</v>
       </c>
@@ -6984,8 +7352,14 @@
       <c r="K61" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1449</v>
       </c>
@@ -7020,8 +7394,14 @@
       <c r="K62" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1449</v>
       </c>
@@ -7056,8 +7436,14 @@
       <c r="K63" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1449</v>
       </c>
@@ -7092,8 +7478,14 @@
       <c r="K64" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1449</v>
       </c>
@@ -7128,8 +7520,14 @@
       <c r="K65" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1449</v>
       </c>
@@ -7164,8 +7562,14 @@
       <c r="K66" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1449</v>
       </c>
@@ -7200,8 +7604,14 @@
       <c r="K67" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1449</v>
       </c>
@@ -7236,8 +7646,14 @@
       <c r="K68" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1449</v>
       </c>
@@ -7272,8 +7688,14 @@
       <c r="K69" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1449</v>
       </c>
@@ -7308,8 +7730,14 @@
       <c r="K70" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1449</v>
       </c>
@@ -7344,8 +7772,14 @@
       <c r="K71" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1449</v>
       </c>
@@ -7380,8 +7814,14 @@
       <c r="K72" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L72" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>1449</v>
       </c>
@@ -7416,8 +7856,14 @@
       <c r="K73" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1449</v>
       </c>
@@ -7452,8 +7898,14 @@
       <c r="K74" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L74" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1449</v>
       </c>
@@ -7488,8 +7940,14 @@
       <c r="K75" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L75" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1449</v>
       </c>
@@ -7524,8 +7982,14 @@
       <c r="K76" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L76" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1449</v>
       </c>
@@ -7560,8 +8024,14 @@
       <c r="K77" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L77" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1449</v>
       </c>
@@ -7596,8 +8066,14 @@
       <c r="K78" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L78" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1449</v>
       </c>
@@ -7632,8 +8108,14 @@
       <c r="K79" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L79" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1449</v>
       </c>
@@ -7668,8 +8150,14 @@
       <c r="K80" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L80" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1449</v>
       </c>
@@ -7704,8 +8192,14 @@
       <c r="K81" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L81" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1449</v>
       </c>
@@ -7740,8 +8234,14 @@
       <c r="K82" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L82" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1449</v>
       </c>
@@ -7776,8 +8276,14 @@
       <c r="K83" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L83" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1450</v>
       </c>
@@ -7812,8 +8318,14 @@
       <c r="K84" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L84" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1450</v>
       </c>
@@ -7848,8 +8360,14 @@
       <c r="K85" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L85" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1450</v>
       </c>
@@ -7884,8 +8402,14 @@
       <c r="K86" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L86" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1450</v>
       </c>
@@ -7920,8 +8444,14 @@
       <c r="K87" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L87" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1450</v>
       </c>
@@ -7956,8 +8486,14 @@
       <c r="K88" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L88" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1450</v>
       </c>
@@ -7992,8 +8528,14 @@
       <c r="K89" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L89" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1450</v>
       </c>
@@ -8028,8 +8570,14 @@
       <c r="K90" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L90" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1450</v>
       </c>
@@ -8064,8 +8612,14 @@
       <c r="K91" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L91" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1450</v>
       </c>
@@ -8100,8 +8654,14 @@
       <c r="K92" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L92" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1450</v>
       </c>
@@ -8136,8 +8696,14 @@
       <c r="K93" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L93" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1450</v>
       </c>
@@ -8172,8 +8738,14 @@
       <c r="K94" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L94" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1450</v>
       </c>
@@ -8208,8 +8780,14 @@
       <c r="K95" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L95" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1450</v>
       </c>
@@ -8244,8 +8822,14 @@
       <c r="K96" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L96" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1450</v>
       </c>
@@ -8280,8 +8864,14 @@
       <c r="K97" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L97" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1450</v>
       </c>
@@ -8316,8 +8906,14 @@
       <c r="K98" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L98" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1450</v>
       </c>
@@ -8352,8 +8948,14 @@
       <c r="K99" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1450</v>
       </c>
@@ -8388,8 +8990,14 @@
       <c r="K100" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1450</v>
       </c>
@@ -8424,8 +9032,14 @@
       <c r="K101" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1450</v>
       </c>
@@ -8460,8 +9074,14 @@
       <c r="K102" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1450</v>
       </c>
@@ -8496,8 +9116,14 @@
       <c r="K103" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1450</v>
       </c>
@@ -8532,8 +9158,14 @@
       <c r="K104" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1450</v>
       </c>
@@ -8568,8 +9200,14 @@
       <c r="K105" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1450</v>
       </c>
@@ -8604,8 +9242,14 @@
       <c r="K106" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L106" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1450</v>
       </c>
@@ -8640,8 +9284,14 @@
       <c r="K107" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L107" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1450</v>
       </c>
@@ -8676,8 +9326,14 @@
       <c r="K108" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L108" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1450</v>
       </c>
@@ -8712,8 +9368,14 @@
       <c r="K109" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L109" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1450</v>
       </c>
@@ -8748,8 +9410,14 @@
       <c r="K110" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L110" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1451</v>
       </c>
@@ -8784,8 +9452,14 @@
       <c r="K111" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L111" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1451</v>
       </c>
@@ -8820,8 +9494,14 @@
       <c r="K112" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L112" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1451</v>
       </c>
@@ -8856,8 +9536,14 @@
       <c r="K113" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L113" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1451</v>
       </c>
@@ -8892,8 +9578,14 @@
       <c r="K114" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L114" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1451</v>
       </c>
@@ -8928,8 +9620,14 @@
       <c r="K115" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L115" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1451</v>
       </c>
@@ -8964,8 +9662,14 @@
       <c r="K116" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L116" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1451</v>
       </c>
@@ -9000,8 +9704,14 @@
       <c r="K117" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L117" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1451</v>
       </c>
@@ -9036,8 +9746,14 @@
       <c r="K118" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L118" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1451</v>
       </c>
@@ -9072,8 +9788,14 @@
       <c r="K119" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L119" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1451</v>
       </c>
@@ -9108,8 +9830,14 @@
       <c r="K120" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L120" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1451</v>
       </c>
@@ -9144,8 +9872,14 @@
       <c r="K121" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L121" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1451</v>
       </c>
@@ -9180,8 +9914,14 @@
       <c r="K122" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L122" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1451</v>
       </c>
@@ -9216,8 +9956,14 @@
       <c r="K123" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L123" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1451</v>
       </c>
@@ -9252,8 +9998,14 @@
       <c r="K124" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L124" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1451</v>
       </c>
@@ -9288,8 +10040,14 @@
       <c r="K125" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L125" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1451</v>
       </c>
@@ -9324,8 +10082,14 @@
       <c r="K126" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L126" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1451</v>
       </c>
@@ -9360,8 +10124,14 @@
       <c r="K127" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L127" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1451</v>
       </c>
@@ -9396,8 +10166,14 @@
       <c r="K128" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L128" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1451</v>
       </c>
@@ -9432,8 +10208,14 @@
       <c r="K129" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L129" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1451</v>
       </c>
@@ -9468,8 +10250,14 @@
       <c r="K130" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L130" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1451</v>
       </c>
@@ -9504,8 +10292,14 @@
       <c r="K131" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L131" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1451</v>
       </c>
@@ -9540,8 +10334,14 @@
       <c r="K132" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L132" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1451</v>
       </c>
@@ -9576,8 +10376,14 @@
       <c r="K133" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L133" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1451</v>
       </c>
@@ -9612,8 +10418,14 @@
       <c r="K134" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L134" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1451</v>
       </c>
@@ -9648,8 +10460,14 @@
       <c r="K135" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L135" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1451</v>
       </c>
@@ -9684,8 +10502,14 @@
       <c r="K136" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L136" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1451</v>
       </c>
@@ -9720,8 +10544,14 @@
       <c r="K137" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L137" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1452</v>
       </c>
@@ -9756,8 +10586,14 @@
       <c r="K138" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L138" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1452</v>
       </c>
@@ -9792,8 +10628,14 @@
       <c r="K139" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L139" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1452</v>
       </c>
@@ -9828,8 +10670,14 @@
       <c r="K140" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L140" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1452</v>
       </c>
@@ -9864,8 +10712,14 @@
       <c r="K141" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L141" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1452</v>
       </c>
@@ -9900,8 +10754,14 @@
       <c r="K142" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L142" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1452</v>
       </c>
@@ -9936,8 +10796,14 @@
       <c r="K143" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L143" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M143" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1452</v>
       </c>
@@ -9972,8 +10838,14 @@
       <c r="K144" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L144" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1452</v>
       </c>
@@ -10008,8 +10880,14 @@
       <c r="K145" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L145" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1452</v>
       </c>
@@ -10044,8 +10922,14 @@
       <c r="K146" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L146" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1452</v>
       </c>
@@ -10080,8 +10964,14 @@
       <c r="K147" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L147" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1452</v>
       </c>
@@ -10116,8 +11006,14 @@
       <c r="K148" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L148" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1452</v>
       </c>
@@ -10152,8 +11048,14 @@
       <c r="K149" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L149" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1452</v>
       </c>
@@ -10188,8 +11090,14 @@
       <c r="K150" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L150" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1452</v>
       </c>
@@ -10224,8 +11132,14 @@
       <c r="K151" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L151" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M151" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1452</v>
       </c>
@@ -10260,8 +11174,14 @@
       <c r="K152" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L152" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1452</v>
       </c>
@@ -10296,8 +11216,14 @@
       <c r="K153" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L153" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1452</v>
       </c>
@@ -10332,8 +11258,14 @@
       <c r="K154" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L154" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1452</v>
       </c>
@@ -10368,8 +11300,14 @@
       <c r="K155" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L155" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M155" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1452</v>
       </c>
@@ -10404,8 +11342,14 @@
       <c r="K156" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L156" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1452</v>
       </c>
@@ -10440,8 +11384,14 @@
       <c r="K157" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L157" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1452</v>
       </c>
@@ -10476,8 +11426,14 @@
       <c r="K158" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L158" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1452</v>
       </c>
@@ -10512,8 +11468,14 @@
       <c r="K159" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L159" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1452</v>
       </c>
@@ -10548,8 +11510,14 @@
       <c r="K160" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L160" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1452</v>
       </c>
@@ -10584,8 +11552,14 @@
       <c r="K161" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L161" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1452</v>
       </c>
@@ -10620,8 +11594,14 @@
       <c r="K162" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L162" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1452</v>
       </c>
@@ -10656,8 +11636,14 @@
       <c r="K163" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L163" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1452</v>
       </c>
@@ -10692,8 +11678,14 @@
       <c r="K164" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L164" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1453</v>
       </c>
@@ -10728,8 +11720,14 @@
       <c r="K165" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L165" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1453</v>
       </c>
@@ -10764,8 +11762,14 @@
       <c r="K166" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L166" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1453</v>
       </c>
@@ -10800,8 +11804,14 @@
       <c r="K167" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L167" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1453</v>
       </c>
@@ -10836,8 +11846,14 @@
       <c r="K168" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L168" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1453</v>
       </c>
@@ -10872,8 +11888,14 @@
       <c r="K169" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L169" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>1453</v>
       </c>
@@ -10908,8 +11930,14 @@
       <c r="K170" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L170" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1453</v>
       </c>
@@ -10944,8 +11972,14 @@
       <c r="K171" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L171" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1453</v>
       </c>
@@ -10980,8 +12014,14 @@
       <c r="K172" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L172" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M172" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1453</v>
       </c>
@@ -11016,8 +12056,14 @@
       <c r="K173" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L173" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1453</v>
       </c>
@@ -11052,8 +12098,14 @@
       <c r="K174" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L174" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1453</v>
       </c>
@@ -11088,8 +12140,14 @@
       <c r="K175" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L175" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>1453</v>
       </c>
@@ -11124,8 +12182,14 @@
       <c r="K176" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L176" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1453</v>
       </c>
@@ -11160,8 +12224,14 @@
       <c r="K177" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L177" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M177" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1453</v>
       </c>
@@ -11196,8 +12266,14 @@
       <c r="K178" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L178" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1453</v>
       </c>
@@ -11232,8 +12308,14 @@
       <c r="K179" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L179" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1453</v>
       </c>
@@ -11268,8 +12350,14 @@
       <c r="K180" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L180" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M180" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1453</v>
       </c>
@@ -11304,8 +12392,14 @@
       <c r="K181" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L181" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M181" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1453</v>
       </c>
@@ -11340,8 +12434,14 @@
       <c r="K182" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L182" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1453</v>
       </c>
@@ -11376,8 +12476,14 @@
       <c r="K183" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L183" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M183" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1453</v>
       </c>
@@ -11412,8 +12518,14 @@
       <c r="K184" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L184" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M184" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1453</v>
       </c>
@@ -11448,8 +12560,14 @@
       <c r="K185" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L185" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1453</v>
       </c>
@@ -11484,8 +12602,14 @@
       <c r="K186" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L186" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1453</v>
       </c>
@@ -11520,8 +12644,14 @@
       <c r="K187" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L187" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1454</v>
       </c>
@@ -11556,8 +12686,14 @@
       <c r="K188" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L188" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1454</v>
       </c>
@@ -11592,8 +12728,14 @@
       <c r="K189" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L189" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1454</v>
       </c>
@@ -11628,8 +12770,14 @@
       <c r="K190" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L190" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1454</v>
       </c>
@@ -11664,8 +12812,14 @@
       <c r="K191" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L191" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1454</v>
       </c>
@@ -11700,8 +12854,14 @@
       <c r="K192" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L192" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1454</v>
       </c>
@@ -11736,8 +12896,14 @@
       <c r="K193" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L193" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1454</v>
       </c>
@@ -11772,8 +12938,14 @@
       <c r="K194" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L194" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1454</v>
       </c>
@@ -11808,8 +12980,14 @@
       <c r="K195" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L195" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1454</v>
       </c>
@@ -11844,8 +13022,14 @@
       <c r="K196" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L196" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1454</v>
       </c>
@@ -11880,8 +13064,14 @@
       <c r="K197" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L197" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1454</v>
       </c>
@@ -11916,8 +13106,14 @@
       <c r="K198" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L198" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1454</v>
       </c>
@@ -11952,8 +13148,14 @@
       <c r="K199" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L199" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M199" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1454</v>
       </c>
@@ -11988,8 +13190,14 @@
       <c r="K200" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L200" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M200" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1454</v>
       </c>
@@ -12024,8 +13232,14 @@
       <c r="K201" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L201" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M201" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1454</v>
       </c>
@@ -12060,8 +13274,14 @@
       <c r="K202" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L202" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M202" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1454</v>
       </c>
@@ -12096,8 +13316,14 @@
       <c r="K203" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L203" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M203" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1454</v>
       </c>
@@ -12132,8 +13358,14 @@
       <c r="K204" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L204" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M204" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1454</v>
       </c>
@@ -12168,8 +13400,14 @@
       <c r="K205" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L205" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M205" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1454</v>
       </c>
@@ -12204,8 +13442,14 @@
       <c r="K206" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L206" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1454</v>
       </c>
@@ -12240,8 +13484,14 @@
       <c r="K207" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L207" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1454</v>
       </c>
@@ -12276,8 +13526,14 @@
       <c r="K208" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L208" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M208" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1454</v>
       </c>
@@ -12312,8 +13568,14 @@
       <c r="K209" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L209" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M209" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1454</v>
       </c>
@@ -12348,8 +13610,14 @@
       <c r="K210" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L210" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M210" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1455</v>
       </c>
@@ -12384,8 +13652,14 @@
       <c r="K211" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L211" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M211" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1455</v>
       </c>
@@ -12420,8 +13694,14 @@
       <c r="K212" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L212" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M212" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1455</v>
       </c>
@@ -12456,8 +13736,14 @@
       <c r="K213" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L213" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M213" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1455</v>
       </c>
@@ -12492,8 +13778,14 @@
       <c r="K214" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L214" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M214" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1455</v>
       </c>
@@ -12528,8 +13820,14 @@
       <c r="K215" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L215" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M215" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1455</v>
       </c>
@@ -12564,8 +13862,14 @@
       <c r="K216" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L216" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M216" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1455</v>
       </c>
@@ -12600,8 +13904,14 @@
       <c r="K217" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L217" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M217" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1455</v>
       </c>
@@ -12636,8 +13946,14 @@
       <c r="K218" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L218" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M218" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1455</v>
       </c>
@@ -12672,8 +13988,14 @@
       <c r="K219" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L219" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M219" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1455</v>
       </c>
@@ -12708,8 +14030,14 @@
       <c r="K220" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L220" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1455</v>
       </c>
@@ -12744,8 +14072,14 @@
       <c r="K221" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L221" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1455</v>
       </c>
@@ -12780,8 +14114,14 @@
       <c r="K222" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L222" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M222" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1455</v>
       </c>
@@ -12816,8 +14156,14 @@
       <c r="K223" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L223" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M223" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1455</v>
       </c>
@@ -12852,8 +14198,14 @@
       <c r="K224" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L224" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M224" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1455</v>
       </c>
@@ -12888,8 +14240,14 @@
       <c r="K225" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L225" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1455</v>
       </c>
@@ -12924,8 +14282,14 @@
       <c r="K226" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L226" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M226" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1455</v>
       </c>
@@ -12960,8 +14324,14 @@
       <c r="K227" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L227" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M227" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1455</v>
       </c>
@@ -12996,8 +14366,14 @@
       <c r="K228" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L228" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M228" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1455</v>
       </c>
@@ -13032,8 +14408,14 @@
       <c r="K229" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L229" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1455</v>
       </c>
@@ -13068,8 +14450,14 @@
       <c r="K230" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L230" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M230" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1455</v>
       </c>
@@ -13104,8 +14492,14 @@
       <c r="K231" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L231" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1455</v>
       </c>
@@ -13140,8 +14534,14 @@
       <c r="K232" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L232" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1457</v>
       </c>
@@ -13176,8 +14576,14 @@
       <c r="K233" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L233" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M233" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1457</v>
       </c>
@@ -13212,8 +14618,14 @@
       <c r="K234" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L234" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1457</v>
       </c>
@@ -13248,8 +14660,14 @@
       <c r="K235" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L235" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M235" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1457</v>
       </c>
@@ -13284,8 +14702,14 @@
       <c r="K236" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L236" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M236" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1457</v>
       </c>
@@ -13320,8 +14744,14 @@
       <c r="K237" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L237" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M237" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1457</v>
       </c>
@@ -13356,8 +14786,14 @@
       <c r="K238" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L238" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M238" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1457</v>
       </c>
@@ -13392,8 +14828,14 @@
       <c r="K239" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L239" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M239" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1457</v>
       </c>
@@ -13428,8 +14870,14 @@
       <c r="K240" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L240" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M240" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1457</v>
       </c>
@@ -13464,8 +14912,14 @@
       <c r="K241" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L241" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M241" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1457</v>
       </c>
@@ -13500,8 +14954,14 @@
       <c r="K242" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L242" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M242" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1457</v>
       </c>
@@ -13536,8 +14996,14 @@
       <c r="K243" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L243" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M243" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1457</v>
       </c>
@@ -13572,8 +15038,14 @@
       <c r="K244" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L244" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M244" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1457</v>
       </c>
@@ -13608,8 +15080,14 @@
       <c r="K245" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L245" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M245" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1457</v>
       </c>
@@ -13644,8 +15122,14 @@
       <c r="K246" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L246" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M246" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1457</v>
       </c>
@@ -13680,8 +15164,14 @@
       <c r="K247" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L247" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M247" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1457</v>
       </c>
@@ -13716,8 +15206,14 @@
       <c r="K248" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L248" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M248" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1457</v>
       </c>
@@ -13752,8 +15248,14 @@
       <c r="K249" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L249" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M249" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1457</v>
       </c>
@@ -13788,8 +15290,14 @@
       <c r="K250" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L250" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M250" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1457</v>
       </c>
@@ -13824,8 +15332,14 @@
       <c r="K251" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L251" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M251" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1457</v>
       </c>
@@ -13860,8 +15374,14 @@
       <c r="K252" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L252" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M252" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1457</v>
       </c>
@@ -13896,8 +15416,14 @@
       <c r="K253" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L253" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M253" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1457</v>
       </c>
@@ -13932,8 +15458,14 @@
       <c r="K254" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L254" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M254" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1457</v>
       </c>
@@ -13968,8 +15500,14 @@
       <c r="K255" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L255" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M255" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1457</v>
       </c>
@@ -14004,8 +15542,14 @@
       <c r="K256" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L256" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M256" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1457</v>
       </c>
@@ -14040,8 +15584,14 @@
       <c r="K257" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L257" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M257" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1456</v>
       </c>
@@ -14076,8 +15626,14 @@
       <c r="K258" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L258" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M258" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1456</v>
       </c>
@@ -14112,8 +15668,14 @@
       <c r="K259" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L259" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M259" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1456</v>
       </c>
@@ -14148,8 +15710,14 @@
       <c r="K260" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L260" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M260" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1456</v>
       </c>
@@ -14184,8 +15752,14 @@
       <c r="K261" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L261" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M261" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1456</v>
       </c>
@@ -14220,8 +15794,14 @@
       <c r="K262" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L262" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M262" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1456</v>
       </c>
@@ -14256,8 +15836,14 @@
       <c r="K263" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L263" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M263" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1456</v>
       </c>
@@ -14292,8 +15878,14 @@
       <c r="K264" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L264" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M264" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1456</v>
       </c>
@@ -14328,8 +15920,14 @@
       <c r="K265" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L265" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M265" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1456</v>
       </c>
@@ -14364,8 +15962,14 @@
       <c r="K266" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L266" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M266" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1456</v>
       </c>
@@ -14400,8 +16004,14 @@
       <c r="K267" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L267" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M267" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1456</v>
       </c>
@@ -14436,8 +16046,14 @@
       <c r="K268" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L268" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M268" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1456</v>
       </c>
@@ -14472,8 +16088,14 @@
       <c r="K269" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L269" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M269" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1456</v>
       </c>
@@ -14508,8 +16130,14 @@
       <c r="K270" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L270" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M270" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1456</v>
       </c>
@@ -14544,8 +16172,14 @@
       <c r="K271" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L271" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M271" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1456</v>
       </c>
@@ -14580,8 +16214,14 @@
       <c r="K272" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L272" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M272" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1456</v>
       </c>
@@ -14616,8 +16256,14 @@
       <c r="K273" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L273" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M273" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1456</v>
       </c>
@@ -14652,8 +16298,14 @@
       <c r="K274" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L274" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M274" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1456</v>
       </c>
@@ -14688,8 +16340,14 @@
       <c r="K275" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L275" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M275" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1456</v>
       </c>
@@ -14724,8 +16382,14 @@
       <c r="K276" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L276" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M276" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1456</v>
       </c>
@@ -14760,8 +16424,14 @@
       <c r="K277" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L277" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M277" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1456</v>
       </c>
@@ -14796,8 +16466,14 @@
       <c r="K278" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L278" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M278" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1456</v>
       </c>
@@ -14832,8 +16508,14 @@
       <c r="K279" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L279" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M279" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1456</v>
       </c>
@@ -14868,8 +16550,14 @@
       <c r="K280" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L280" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M280" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1456</v>
       </c>
@@ -14904,8 +16592,14 @@
       <c r="K281" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L281" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M281" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1456</v>
       </c>
@@ -14940,8 +16634,14 @@
       <c r="K282" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L282" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M282" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1458</v>
       </c>
@@ -14976,8 +16676,14 @@
       <c r="K283" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L283" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M283" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1458</v>
       </c>
@@ -15012,8 +16718,14 @@
       <c r="K284" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L284" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M284" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1458</v>
       </c>
@@ -15048,8 +16760,14 @@
       <c r="K285" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L285" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M285" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1458</v>
       </c>
@@ -15084,8 +16802,14 @@
       <c r="K286" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L286" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M286" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1458</v>
       </c>
@@ -15120,8 +16844,14 @@
       <c r="K287" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L287" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M287" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1458</v>
       </c>
@@ -15156,8 +16886,14 @@
       <c r="K288" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L288" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M288" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1458</v>
       </c>
@@ -15192,8 +16928,14 @@
       <c r="K289" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L289" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M289" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1458</v>
       </c>
@@ -15228,8 +16970,14 @@
       <c r="K290" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L290" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M290" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1458</v>
       </c>
@@ -15264,8 +17012,14 @@
       <c r="K291" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L291" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M291" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1458</v>
       </c>
@@ -15300,8 +17054,14 @@
       <c r="K292" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L292" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M292" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1458</v>
       </c>
@@ -15336,8 +17096,14 @@
       <c r="K293" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L293" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M293" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1458</v>
       </c>
@@ -15372,8 +17138,14 @@
       <c r="K294" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L294" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M294" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1458</v>
       </c>
@@ -15408,8 +17180,14 @@
       <c r="K295" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L295" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M295" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1458</v>
       </c>
@@ -15444,8 +17222,14 @@
       <c r="K296" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L296" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M296" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1458</v>
       </c>
@@ -15480,8 +17264,14 @@
       <c r="K297" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L297" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M297" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1458</v>
       </c>
@@ -15516,8 +17306,14 @@
       <c r="K298" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L298" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M298" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1458</v>
       </c>
@@ -15552,8 +17348,14 @@
       <c r="K299" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L299" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M299" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1458</v>
       </c>
@@ -15588,8 +17390,14 @@
       <c r="K300" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L300" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M300" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1458</v>
       </c>
@@ -15624,8 +17432,14 @@
       <c r="K301" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L301" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M301" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1458</v>
       </c>
@@ -15660,8 +17474,14 @@
       <c r="K302" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L302" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M302" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1458</v>
       </c>
@@ -15696,8 +17516,14 @@
       <c r="K303" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L303" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M303" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1458</v>
       </c>
@@ -15732,8 +17558,14 @@
       <c r="K304" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L304" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M304" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1458</v>
       </c>
@@ -15768,8 +17600,14 @@
       <c r="K305" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L305" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M305" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1458</v>
       </c>
@@ -15804,8 +17642,14 @@
       <c r="K306" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L306" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M306" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1458</v>
       </c>
@@ -15840,8 +17684,14 @@
       <c r="K307" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L307" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M307" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1458</v>
       </c>
@@ -15876,8 +17726,14 @@
       <c r="K308" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L308" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M308" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1458</v>
       </c>
@@ -15912,8 +17768,14 @@
       <c r="K309" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L309" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M309" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1458</v>
       </c>
@@ -15948,8 +17810,14 @@
       <c r="K310" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L310" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M310" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1459</v>
       </c>
@@ -15984,8 +17852,14 @@
       <c r="K311" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L311" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M311" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1459</v>
       </c>
@@ -16020,8 +17894,14 @@
       <c r="K312" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L312" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M312" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1459</v>
       </c>
@@ -16056,8 +17936,14 @@
       <c r="K313" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L313" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M313" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1459</v>
       </c>
@@ -16092,8 +17978,14 @@
       <c r="K314" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L314" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M314" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1459</v>
       </c>
@@ -16128,8 +18020,14 @@
       <c r="K315" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L315" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M315" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1459</v>
       </c>
@@ -16164,8 +18062,14 @@
       <c r="K316" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L316" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M316" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1459</v>
       </c>
@@ -16200,8 +18104,14 @@
       <c r="K317" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L317" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M317" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1459</v>
       </c>
@@ -16236,8 +18146,14 @@
       <c r="K318" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L318" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M318" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1459</v>
       </c>
@@ -16272,8 +18188,14 @@
       <c r="K319" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L319" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M319" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1459</v>
       </c>
@@ -16308,8 +18230,14 @@
       <c r="K320" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L320" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M320" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1459</v>
       </c>
@@ -16344,8 +18272,14 @@
       <c r="K321" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L321" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M321" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1459</v>
       </c>
@@ -16380,8 +18314,14 @@
       <c r="K322" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L322" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M322" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1459</v>
       </c>
@@ -16416,8 +18356,14 @@
       <c r="K323" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L323" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M323" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1459</v>
       </c>
@@ -16452,8 +18398,14 @@
       <c r="K324" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L324" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M324" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1459</v>
       </c>
@@ -16488,8 +18440,14 @@
       <c r="K325" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L325" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M325" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1459</v>
       </c>
@@ -16524,8 +18482,14 @@
       <c r="K326" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L326" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M326" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1459</v>
       </c>
@@ -16560,8 +18524,14 @@
       <c r="K327" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L327" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M327" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1459</v>
       </c>
@@ -16596,8 +18566,14 @@
       <c r="K328" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L328" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M328" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1459</v>
       </c>
@@ -16632,8 +18608,14 @@
       <c r="K329" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L329" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M329" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1459</v>
       </c>
@@ -16668,8 +18650,14 @@
       <c r="K330" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L330" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M330" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1459</v>
       </c>
@@ -16704,8 +18692,14 @@
       <c r="K331" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L331" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M331" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1460</v>
       </c>
@@ -16740,8 +18734,14 @@
       <c r="K332" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L332" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M332" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1460</v>
       </c>
@@ -16776,8 +18776,14 @@
       <c r="K333" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L333" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M333" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1460</v>
       </c>
@@ -16812,8 +18818,14 @@
       <c r="K334" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L334" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M334" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1460</v>
       </c>
@@ -16848,8 +18860,14 @@
       <c r="K335" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L335" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M335" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1460</v>
       </c>
@@ -16884,8 +18902,14 @@
       <c r="K336" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L336" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M336" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1460</v>
       </c>
@@ -16920,8 +18944,14 @@
       <c r="K337" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L337" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M337" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1460</v>
       </c>
@@ -16956,8 +18986,14 @@
       <c r="K338" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L338" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M338" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1460</v>
       </c>
@@ -16992,8 +19028,14 @@
       <c r="K339" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L339" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M339" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1460</v>
       </c>
@@ -17028,8 +19070,14 @@
       <c r="K340" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L340" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M340" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1460</v>
       </c>
@@ -17064,8 +19112,14 @@
       <c r="K341" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L341" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M341" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1460</v>
       </c>
@@ -17100,8 +19154,14 @@
       <c r="K342" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L342" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M342" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1460</v>
       </c>
@@ -17136,8 +19196,14 @@
       <c r="K343" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L343" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M343" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1460</v>
       </c>
@@ -17172,8 +19238,14 @@
       <c r="K344" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L344" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M344" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1460</v>
       </c>
@@ -17208,8 +19280,14 @@
       <c r="K345" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L345" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M345" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1460</v>
       </c>
@@ -17244,8 +19322,14 @@
       <c r="K346" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L346" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M346" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1460</v>
       </c>
@@ -17280,8 +19364,14 @@
       <c r="K347" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L347" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M347" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1460</v>
       </c>
@@ -17316,8 +19406,14 @@
       <c r="K348" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L348" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M348" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1460</v>
       </c>
@@ -17352,8 +19448,14 @@
       <c r="K349" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L349" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M349" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1460</v>
       </c>
@@ -17388,8 +19490,14 @@
       <c r="K350" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L350" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M350" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1460</v>
       </c>
@@ -17424,8 +19532,14 @@
       <c r="K351" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L351" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M351" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1460</v>
       </c>
@@ -17460,8 +19574,14 @@
       <c r="K352" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L352" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M352" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1461</v>
       </c>
@@ -17496,8 +19616,14 @@
       <c r="K353" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L353" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M353" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1461</v>
       </c>
@@ -17532,8 +19658,14 @@
       <c r="K354" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L354" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M354" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1461</v>
       </c>
@@ -17568,8 +19700,14 @@
       <c r="K355" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L355" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M355" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1461</v>
       </c>
@@ -17604,8 +19742,14 @@
       <c r="K356" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L356" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M356" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1461</v>
       </c>
@@ -17640,8 +19784,14 @@
       <c r="K357" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L357" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M357" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1461</v>
       </c>
@@ -17676,8 +19826,14 @@
       <c r="K358" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L358" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M358" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1461</v>
       </c>
@@ -17712,8 +19868,14 @@
       <c r="K359" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L359" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M359" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1461</v>
       </c>
@@ -17748,8 +19910,14 @@
       <c r="K360" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L360" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M360" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1461</v>
       </c>
@@ -17784,8 +19952,14 @@
       <c r="K361" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L361" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M361" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1461</v>
       </c>
@@ -17820,8 +19994,14 @@
       <c r="K362" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L362" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M362" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1461</v>
       </c>
@@ -17856,8 +20036,14 @@
       <c r="K363" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L363" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M363" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1461</v>
       </c>
@@ -17892,8 +20078,14 @@
       <c r="K364" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L364" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M364" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1461</v>
       </c>
@@ -17928,8 +20120,14 @@
       <c r="K365" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L365" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M365" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1461</v>
       </c>
@@ -17964,8 +20162,14 @@
       <c r="K366" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L366" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M366" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1461</v>
       </c>
@@ -18000,8 +20204,14 @@
       <c r="K367" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L367" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M367" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1461</v>
       </c>
@@ -18036,8 +20246,14 @@
       <c r="K368" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L368" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M368" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1461</v>
       </c>
@@ -18072,8 +20288,14 @@
       <c r="K369" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L369" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M369" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1461</v>
       </c>
@@ -18108,8 +20330,14 @@
       <c r="K370" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L370" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M370" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1461</v>
       </c>
@@ -18144,8 +20372,14 @@
       <c r="K371" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L371" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M371" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1461</v>
       </c>
@@ -18180,8 +20414,14 @@
       <c r="K372" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L372" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M372" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1461</v>
       </c>
@@ -18216,8 +20456,14 @@
       <c r="K373" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L373" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M373" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1461</v>
       </c>
@@ -18252,8 +20498,14 @@
       <c r="K374" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L374" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M374" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1461</v>
       </c>
@@ -18288,8 +20540,14 @@
       <c r="K375" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L375" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M375" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1462</v>
       </c>
@@ -18324,8 +20582,14 @@
       <c r="K376" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L376" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M376" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1462</v>
       </c>
@@ -18360,8 +20624,14 @@
       <c r="K377" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L377" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M377" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1462</v>
       </c>
@@ -18396,8 +20666,14 @@
       <c r="K378" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L378" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M378" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1462</v>
       </c>
@@ -18432,8 +20708,14 @@
       <c r="K379" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L379" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M379" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1462</v>
       </c>
@@ -18468,8 +20750,14 @@
       <c r="K380" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L380" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M380" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1462</v>
       </c>
@@ -18504,8 +20792,14 @@
       <c r="K381" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L381" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M381" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1462</v>
       </c>
@@ -18540,8 +20834,14 @@
       <c r="K382" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L382" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M382" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1462</v>
       </c>
@@ -18576,8 +20876,14 @@
       <c r="K383" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L383" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M383" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1462</v>
       </c>
@@ -18612,8 +20918,14 @@
       <c r="K384" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L384" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M384" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1462</v>
       </c>
@@ -18648,8 +20960,14 @@
       <c r="K385" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L385" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M385" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1462</v>
       </c>
@@ -18684,8 +21002,14 @@
       <c r="K386" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L386" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M386" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1462</v>
       </c>
@@ -18720,8 +21044,14 @@
       <c r="K387" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L387" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M387" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1462</v>
       </c>
@@ -18756,8 +21086,14 @@
       <c r="K388" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L388" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M388" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1462</v>
       </c>
@@ -18792,8 +21128,14 @@
       <c r="K389" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L389" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M389" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1462</v>
       </c>
@@ -18828,8 +21170,14 @@
       <c r="K390" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L390" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M390" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1462</v>
       </c>
@@ -18864,8 +21212,14 @@
       <c r="K391" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L391" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M391" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1462</v>
       </c>
@@ -18900,8 +21254,14 @@
       <c r="K392" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L392" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M392" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1462</v>
       </c>
@@ -18936,8 +21296,14 @@
       <c r="K393" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L393" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M393" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1462</v>
       </c>
@@ -18972,8 +21338,14 @@
       <c r="K394" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L394" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M394" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1462</v>
       </c>
@@ -19008,8 +21380,14 @@
       <c r="K395" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L395" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M395" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1462</v>
       </c>
@@ -19044,8 +21422,14 @@
       <c r="K396" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L396" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M396" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1462</v>
       </c>
@@ -19080,8 +21464,14 @@
       <c r="K397" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L397" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M397" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1462</v>
       </c>
@@ -19116,8 +21506,14 @@
       <c r="K398" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L398" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M398" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>73</v>
       </c>
@@ -19152,8 +21548,14 @@
       <c r="K399" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L399" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M399" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>73</v>
       </c>
@@ -19188,8 +21590,14 @@
       <c r="K400" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L400" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M400" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>73</v>
       </c>
@@ -19224,8 +21632,14 @@
       <c r="K401" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L401" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M401" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>73</v>
       </c>
@@ -19260,8 +21674,14 @@
       <c r="K402" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L402" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M402" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>73</v>
       </c>
@@ -19296,8 +21716,14 @@
       <c r="K403" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L403" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M403" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>73</v>
       </c>
@@ -19332,8 +21758,14 @@
       <c r="K404" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L404" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M404" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>73</v>
       </c>
@@ -19368,8 +21800,14 @@
       <c r="K405" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L405" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M405" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>73</v>
       </c>
@@ -19404,8 +21842,14 @@
       <c r="K406" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L406" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M406" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>73</v>
       </c>
@@ -19440,8 +21884,14 @@
       <c r="K407" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L407" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M407" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>73</v>
       </c>
@@ -19476,8 +21926,14 @@
       <c r="K408" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L408" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M408" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>73</v>
       </c>
@@ -19512,8 +21968,14 @@
       <c r="K409" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L409" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M409" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>73</v>
       </c>
@@ -19548,8 +22010,14 @@
       <c r="K410" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L410" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M410" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>73</v>
       </c>
@@ -19584,8 +22052,14 @@
       <c r="K411" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L411" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M411" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>73</v>
       </c>
@@ -19620,8 +22094,14 @@
       <c r="K412" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L412" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M412" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>73</v>
       </c>
@@ -19656,8 +22136,14 @@
       <c r="K413" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L413" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M413" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>73</v>
       </c>
@@ -19692,8 +22178,14 @@
       <c r="K414" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L414" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M414" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>73</v>
       </c>
@@ -19728,8 +22220,14 @@
       <c r="K415" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L415" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M415" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>73</v>
       </c>
@@ -19764,8 +22262,14 @@
       <c r="K416" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L416" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M416" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>73</v>
       </c>
@@ -19800,8 +22304,14 @@
       <c r="K417" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L417" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M417" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>73</v>
       </c>
@@ -19836,8 +22346,14 @@
       <c r="K418" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L418" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M418" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>73</v>
       </c>
@@ -19872,8 +22388,14 @@
       <c r="K419" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L419" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M419" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>74</v>
       </c>
@@ -19908,8 +22430,14 @@
       <c r="K420" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L420" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M420" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>74</v>
       </c>
@@ -19944,8 +22472,14 @@
       <c r="K421" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L421" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M421" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>74</v>
       </c>
@@ -19980,8 +22514,14 @@
       <c r="K422" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L422" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M422" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>74</v>
       </c>
@@ -20016,8 +22556,14 @@
       <c r="K423" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L423" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M423" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>74</v>
       </c>
@@ -20052,8 +22598,14 @@
       <c r="K424" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L424" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M424" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>74</v>
       </c>
@@ -20088,8 +22640,14 @@
       <c r="K425" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L425" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M425" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>74</v>
       </c>
@@ -20124,8 +22682,14 @@
       <c r="K426" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L426" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M426" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>74</v>
       </c>
@@ -20160,8 +22724,14 @@
       <c r="K427" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L427" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M427" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>74</v>
       </c>
@@ -20196,8 +22766,14 @@
       <c r="K428" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L428" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M428" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>74</v>
       </c>
@@ -20232,8 +22808,14 @@
       <c r="K429" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L429" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M429" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>74</v>
       </c>
@@ -20268,8 +22850,14 @@
       <c r="K430" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L430" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M430" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>74</v>
       </c>
@@ -20304,8 +22892,14 @@
       <c r="K431" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L431" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M431" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>74</v>
       </c>
@@ -20340,8 +22934,14 @@
       <c r="K432" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L432" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M432" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>74</v>
       </c>
@@ -20376,8 +22976,14 @@
       <c r="K433" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L433" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M433" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>74</v>
       </c>
@@ -20412,8 +23018,14 @@
       <c r="K434" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L434" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M434" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>74</v>
       </c>
@@ -20448,8 +23060,14 @@
       <c r="K435" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L435" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M435" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>74</v>
       </c>
@@ -20484,8 +23102,14 @@
       <c r="K436" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L436" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M436" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>74</v>
       </c>
@@ -20520,8 +23144,14 @@
       <c r="K437" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L437" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M437" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>74</v>
       </c>
@@ -20556,8 +23186,14 @@
       <c r="K438" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L438" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M438" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>74</v>
       </c>
@@ -20592,8 +23228,14 @@
       <c r="K439" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L439" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M439" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>74</v>
       </c>
@@ -20628,8 +23270,14 @@
       <c r="K440" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L440" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M440" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>74</v>
       </c>
@@ -20664,8 +23312,14 @@
       <c r="K441" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L441" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M441" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>74</v>
       </c>
@@ -20700,8 +23354,14 @@
       <c r="K442" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L442" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M442" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>74</v>
       </c>
@@ -20736,8 +23396,14 @@
       <c r="K443" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L443" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M443" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>74</v>
       </c>
@@ -20772,8 +23438,14 @@
       <c r="K444" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L444" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M444" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>74</v>
       </c>
@@ -20808,8 +23480,14 @@
       <c r="K445" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L445" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M445" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>74</v>
       </c>
@@ -20844,8 +23522,14 @@
       <c r="K446" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L446" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M446" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>74</v>
       </c>
@@ -20880,8 +23564,14 @@
       <c r="K447" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L447" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M447" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>74</v>
       </c>
@@ -20916,8 +23606,14 @@
       <c r="K448" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L448" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M448" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>75</v>
       </c>
@@ -20952,8 +23648,14 @@
       <c r="K449" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L449" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M449" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>75</v>
       </c>
@@ -20988,8 +23690,14 @@
       <c r="K450" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L450" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M450" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>75</v>
       </c>
@@ -21024,8 +23732,14 @@
       <c r="K451" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L451" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M451" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>75</v>
       </c>
@@ -21060,8 +23774,14 @@
       <c r="K452" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L452" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M452" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>75</v>
       </c>
@@ -21096,8 +23816,14 @@
       <c r="K453" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L453" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M453" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>75</v>
       </c>
@@ -21132,8 +23858,14 @@
       <c r="K454" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L454" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M454" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>75</v>
       </c>
@@ -21168,8 +23900,14 @@
       <c r="K455" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L455" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M455" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>75</v>
       </c>
@@ -21204,8 +23942,14 @@
       <c r="K456" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L456" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M456" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>75</v>
       </c>
@@ -21240,8 +23984,14 @@
       <c r="K457" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L457" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M457" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>75</v>
       </c>
@@ -21276,8 +24026,14 @@
       <c r="K458" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L458" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M458" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>75</v>
       </c>
@@ -21312,8 +24068,14 @@
       <c r="K459" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L459" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M459" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>75</v>
       </c>
@@ -21348,8 +24110,14 @@
       <c r="K460" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L460" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M460" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>75</v>
       </c>
@@ -21384,8 +24152,14 @@
       <c r="K461" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L461" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M461" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>75</v>
       </c>
@@ -21420,8 +24194,14 @@
       <c r="K462" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L462" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M462" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>75</v>
       </c>
@@ -21456,8 +24236,14 @@
       <c r="K463" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L463" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M463" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>75</v>
       </c>
@@ -21492,8 +24278,14 @@
       <c r="K464" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L464" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M464" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>75</v>
       </c>
@@ -21528,8 +24320,14 @@
       <c r="K465" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L465" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M465" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>75</v>
       </c>
@@ -21564,8 +24362,14 @@
       <c r="K466" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L466" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M466" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>75</v>
       </c>
@@ -21600,8 +24404,14 @@
       <c r="K467" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L467" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M467" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>75</v>
       </c>
@@ -21636,8 +24446,14 @@
       <c r="K468" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L468" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M468" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>75</v>
       </c>
@@ -21672,8 +24488,14 @@
       <c r="K469" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L469" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M469" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>75</v>
       </c>
@@ -21708,8 +24530,14 @@
       <c r="K470" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L470" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M470" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>75</v>
       </c>
@@ -21744,8 +24572,14 @@
       <c r="K471" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L471" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M471" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>75</v>
       </c>
@@ -21780,8 +24614,14 @@
       <c r="K472" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L472" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M472" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>75</v>
       </c>
@@ -21816,8 +24656,14 @@
       <c r="K473" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L473" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M473" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>75</v>
       </c>
@@ -21852,8 +24698,14 @@
       <c r="K474" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L474" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M474" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>75</v>
       </c>
@@ -21888,8 +24740,14 @@
       <c r="K475" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L475" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M475" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>76</v>
       </c>
@@ -21924,8 +24782,14 @@
       <c r="K476" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L476" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M476" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>76</v>
       </c>
@@ -21960,8 +24824,14 @@
       <c r="K477" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L477" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M477" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>76</v>
       </c>
@@ -21996,8 +24866,14 @@
       <c r="K478" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L478" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M478" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>76</v>
       </c>
@@ -22032,8 +24908,14 @@
       <c r="K479" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L479" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M479" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>76</v>
       </c>
@@ -22068,8 +24950,14 @@
       <c r="K480" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L480" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M480" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>76</v>
       </c>
@@ -22104,8 +24992,14 @@
       <c r="K481" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L481" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M481" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>76</v>
       </c>
@@ -22140,8 +25034,14 @@
       <c r="K482" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L482" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M482" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>76</v>
       </c>
@@ -22176,8 +25076,14 @@
       <c r="K483" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L483" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M483" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>76</v>
       </c>
@@ -22212,8 +25118,14 @@
       <c r="K484" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L484" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M484" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>76</v>
       </c>
@@ -22248,8 +25160,14 @@
       <c r="K485" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L485" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M485" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>76</v>
       </c>
@@ -22284,8 +25202,14 @@
       <c r="K486" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L486" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M486" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>76</v>
       </c>
@@ -22320,8 +25244,14 @@
       <c r="K487" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L487" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M487" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>76</v>
       </c>
@@ -22356,8 +25286,14 @@
       <c r="K488" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L488" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M488" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>76</v>
       </c>
@@ -22392,8 +25328,14 @@
       <c r="K489" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L489" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M489" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>76</v>
       </c>
@@ -22428,8 +25370,14 @@
       <c r="K490" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L490" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M490" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>76</v>
       </c>
@@ -22464,8 +25412,14 @@
       <c r="K491" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L491" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M491" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>76</v>
       </c>
@@ -22500,8 +25454,14 @@
       <c r="K492" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L492" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M492" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>76</v>
       </c>
@@ -22536,8 +25496,14 @@
       <c r="K493" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L493" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M493" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>76</v>
       </c>
@@ -22572,8 +25538,14 @@
       <c r="K494" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L494" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M494" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>76</v>
       </c>
@@ -22608,8 +25580,14 @@
       <c r="K495" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L495" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M495" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>76</v>
       </c>
@@ -22644,8 +25622,14 @@
       <c r="K496" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L496" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M496" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>76</v>
       </c>
@@ -22680,8 +25664,14 @@
       <c r="K497" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L497" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M497" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>76</v>
       </c>
@@ -22716,8 +25706,14 @@
       <c r="K498" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L498" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M498" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>76</v>
       </c>
@@ -22752,8 +25748,14 @@
       <c r="K499" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L499" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M499" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>76</v>
       </c>
@@ -22786,6 +25788,12 @@
         <v>72</v>
       </c>
       <c r="K500" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L500" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M500" s="2" t="s">
         <v>72</v>
       </c>
     </row>

--- a/nilai/data_siswa.xlsx
+++ b/nilai/data_siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\nilai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E62C870-CE19-4758-8D66-9CDA1DD5AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FD1973-12EB-45DC-B7B9-95BA087EF42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94B37993-57FC-457C-970B-6E7EDB0DEC76}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6001" uniqueCount="1466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5993" uniqueCount="1466">
   <si>
     <t>nisn</t>
   </si>
@@ -4856,29 +4856,29 @@
       <c r="E2" t="s">
         <v>1025</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>72</v>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2">
+        <v>60</v>
+      </c>
+      <c r="I2" s="2">
+        <v>40</v>
+      </c>
+      <c r="J2" s="2">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2">
+        <v>90</v>
+      </c>
+      <c r="L2" s="2">
+        <v>60</v>
+      </c>
+      <c r="M2" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
